--- a/KatalonData/RADTestData/Summary.xlsx
+++ b/KatalonData/RADTestData/Summary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\RADTestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{A5BD1B6B-EA73-4EAD-9BF6-5C62A23C4999}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr documentId="13_ncr:1_{134BC73E-D858-4B1B-9596-20070A3695CF}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
-    <workbookView activeTab="3" windowHeight="16776" windowWidth="30936" xWindow="69012" xr2:uid="{D99FAB39-5CE6-4AA4-B9C6-99B1EFA0654E}" yWindow="-108"/>
+    <workbookView activeTab="1" windowHeight="15675" windowWidth="28996" xWindow="-98" xr2:uid="{D99FAB39-5CE6-4AA4-B9C6-99B1EFA0654E}" yWindow="-98"/>
   </bookViews>
   <sheets>
     <sheet name="Estimated" r:id="rId1" sheetId="1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1277" uniqueCount="273">
   <si>
     <t>Result</t>
   </si>
@@ -255,400 +255,616 @@
     <t>Mon Feb 24 19:11:54 EST 2025</t>
   </si>
   <si>
-    <t>Tue Nov 04 17:48:08 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 17:48:31 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 17:48:54 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 17:49:13 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 17:49:31 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 17:49:49 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 18:26:32 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 18:26:55 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 18:27:13 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 18:27:41 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 18:28:18 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 18:29:56 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 18:30:59 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 18:32:37 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 18:32:53 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 18:33:08 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 18:33:53 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 18:34:09 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 18:34:35 EST 2025</t>
-  </si>
-  <si>
     <t>Tue Nov 04 18:35:13 EST 2025</t>
   </si>
   <si>
-    <t>Tue Nov 04 18:42:13 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 18:44:47 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 18:47:04 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 18:47:48 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 18:48:10 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 18:52:50 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 18:53:07 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 18:53:24 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 18:55:02 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 18:56:11 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 18:56:33 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 18:58:51 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 18:59:54 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 19:00:35 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 19:00:53 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 19:01:12 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 19:01:52 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 19:18:33 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 19:19:01 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 19:19:27 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 19:19:53 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 19:20:18 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 20:00:05 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 20:00:26 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 20:01:25 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 20:01:40 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 20:02:03 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 20:02:24 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 20:02:39 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 20:03:52 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 20:04:09 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 20:05:05 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 20:05:36 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 20:07:16 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 20:07:46 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 20:09:42 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 20:11:45 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 20:16:17 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 20:16:34 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 20:16:58 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 20:17:13 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 20:17:46 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 20:19:21 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 20:19:43 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 20:22:50 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 20:23:23 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 20:24:43 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 20:24:59 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 20:27:29 EST 2025</t>
-  </si>
-  <si>
     <t>Tue Nov 04 20:28:06 EST 2025</t>
   </si>
   <si>
-    <t>Tue Nov 04 20:29:46 EST 2025</t>
-  </si>
-  <si>
     <t>Tue Nov 04 20:30:16 EST 2025</t>
   </si>
   <si>
-    <t>Tue Nov 04 21:04:22 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:04:45 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:05:05 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:05:24 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:05:43 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:06:02 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:06:22 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:06:41 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:07:01 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:07:21 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:07:41 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:08:01 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:08:21 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:08:41 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:09:00 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:09:20 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:09:39 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:09:59 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:10:19 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:10:38 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:10:57 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:11:16 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:11:39 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:11:58 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:12:17 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:12:36 EST 2025</t>
-  </si>
-  <si>
     <t>Tue Nov 04 21:12:56 EST 2025</t>
   </si>
   <si>
     <t>This is in QA and Demo but not in Production</t>
   </si>
   <si>
+    <t>2026</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:38:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:39:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:39:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:39:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:40:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:40:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:40:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:41:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:41:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:41:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:41:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:42:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:42:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:42:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:42:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:43:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:43:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:43:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:43:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:44:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:44:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:44:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:44:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:44:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:45:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:45:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:45:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:45:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:46:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:46:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:46:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:47:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:47:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:47:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:48:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:48:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:48:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:49:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:49:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:49:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:50:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:50:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:50:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:51:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:51:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:51:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:52:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:52:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:52:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:53:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:53:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:53:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:54:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:54:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:54:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:55:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:55:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:56:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:56:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:56:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:57:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:57:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:57:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:58:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:58:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:58:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:59:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:59:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 17:59:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 18:00:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 18:00:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 18:01:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 18:01:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 18:01:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 18:02:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 18:02:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 18:02:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 18:03:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 18:03:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 18:03:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 18:04:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 18:04:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 18:04:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 18:05:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 18:05:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 18:05:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 18:06:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 18:06:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 18:07:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 18:07:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 18:07:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 18:08:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 18:08:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 18:09:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 18:09:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 18:10:09 EDT 2026</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>Fail</t>
-  </si>
-  <si>
-    <t>Thu Nov 06 09:38:22 EST 2025</t>
-  </si>
-  <si>
-    <t>Thu Nov 06 09:38:32 EST 2025</t>
-  </si>
-  <si>
-    <t>Thu Nov 06 09:38:39 EST 2025</t>
-  </si>
-  <si>
-    <t>Thu Nov 06 09:38:46 EST 2025</t>
-  </si>
-  <si>
-    <t>Thu Nov 06 09:38:52 EST 2025</t>
-  </si>
-  <si>
-    <t>Thu Nov 06 09:38:58 EST 2025</t>
-  </si>
-  <si>
-    <t>Thu Nov 06 09:39:05 EST 2025</t>
-  </si>
-  <si>
-    <t>Thu Nov 06 09:39:09 EST 2025</t>
-  </si>
-  <si>
-    <t>Thu Nov 06 09:39:12 EST 2025</t>
-  </si>
-  <si>
-    <t>Thu Nov 06 09:39:16 EST 2025</t>
-  </si>
-  <si>
-    <t>Thu Nov 06 09:39:20 EST 2025</t>
-  </si>
-  <si>
-    <t>Thu Nov 06 09:39:24 EST 2025</t>
-  </si>
-  <si>
-    <t>Thu Nov 06 09:39:28 EST 2025</t>
-  </si>
-  <si>
-    <t>Thu Nov 06 09:39:32 EST 2025</t>
-  </si>
-  <si>
-    <t>Thu Nov 06 09:39:36 EST 2025</t>
-  </si>
-  <si>
-    <t>Thu Nov 06 09:39:40 EST 2025</t>
-  </si>
-  <si>
-    <t>Thu Nov 06 09:39:44 EST 2025</t>
-  </si>
-  <si>
-    <t>Thu Nov 06 09:39:53 EST 2025</t>
-  </si>
-  <si>
-    <t>Thu Nov 06 09:39:58 EST 2025</t>
-  </si>
-  <si>
-    <t>Thu Nov 06 09:40:02 EST 2025</t>
-  </si>
-  <si>
-    <t>Thu Nov 06 09:40:07 EST 2025</t>
-  </si>
-  <si>
-    <t>Thu Nov 06 09:40:11 EST 2025</t>
-  </si>
-  <si>
-    <t>Thu Nov 06 09:40:15 EST 2025</t>
-  </si>
-  <si>
-    <t>Thu Nov 06 09:40:19 EST 2025</t>
-  </si>
-  <si>
-    <t>Thu Nov 06 09:40:23 EST 2025</t>
-  </si>
-  <si>
-    <t>Thu Nov 06 09:40:27 EST 2025</t>
-  </si>
-  <si>
-    <t>Thu Nov 06 09:40:31 EST 2025</t>
-  </si>
-  <si>
-    <t>Thu Nov 06 09:40:34 EST 2025</t>
-  </si>
-  <si>
-    <t>Thu Nov 06 09:40:38 EST 2025</t>
-  </si>
-  <si>
-    <t>Thu Nov 06 09:40:42 EST 2025</t>
+    <t>Fri May 29 16:50:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 16:51:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 16:52:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 16:53:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 16:54:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 16:54:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 16:55:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 16:56:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 16:57:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 16:58:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 16:59:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:00:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:01:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:01:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:02:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:03:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:04:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:05:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:06:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:07:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:07:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:08:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:09:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:10:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:11:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:12:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:12:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:13:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:14:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:15:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:16:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:17:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:18:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:19:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:19:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:20:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:21:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:22:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:23:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:24:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:25:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:26:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:27:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:28:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:29:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:30:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:31:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:32:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:33:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:34:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:35:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:36:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:37:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:38:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:39:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:40:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:41:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:41:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:42:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:43:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:44:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:45:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:46:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:47:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:48:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:49:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:50:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:51:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:52:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:53:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:54:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:55:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:56:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:57:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:58:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 17:59:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 18:00:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 18:01:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 18:02:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 18:03:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 18:04:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 18:05:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 18:06:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 18:06:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 18:07:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 18:08:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 18:09:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 18:10:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 18:11:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 18:12:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 18:13:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 18:14:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 18:15:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 18:16:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 18:17:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 18:18:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 18:19:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 18:20:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 18:21:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 18:22:51 EDT 2026</t>
   </si>
 </sst>
 </file>
@@ -1025,22 +1241,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19BDCA51-7A9D-4BB2-A660-F3BEEC814D67}">
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:J8"/>
+  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.1796875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.7265625" collapsed="true"/>
-    <col min="3" max="3" style="1" width="9.1796875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="44.54296875" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="35.54296875" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="1" width="15.26953125" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="1" width="17.26953125" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="1" width="19.54296875" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="1" width="40.1796875" collapsed="true"/>
-    <col min="10" max="16384" style="1" width="9.1796875" collapsed="true"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.73046875" collapsed="true"/>
+    <col min="3" max="3" style="1" width="9.19921875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="44.53125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="35.53125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="1" width="15.265625" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="1" width="17.265625" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="19.53125" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="1" width="40.19921875" collapsed="true"/>
+    <col min="10" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1066,12 +1282,12 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>170</v>
+        <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -1083,7 +1299,7 @@
         <v>8</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>19</v>
@@ -1092,12 +1308,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>170</v>
+        <v>35</v>
       </c>
       <c r="B3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -1109,7 +1325,7 @@
         <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>20</v>
@@ -1118,12 +1334,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>170</v>
+        <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -1135,7 +1351,7 @@
         <v>10</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>21</v>
@@ -1144,12 +1360,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>170</v>
+        <v>35</v>
       </c>
       <c r="B5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -1161,7 +1377,7 @@
         <v>11</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>22</v>
@@ -1170,12 +1386,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>170</v>
+        <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -1187,7 +1403,7 @@
         <v>12</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>23</v>
@@ -1196,12 +1412,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>170</v>
+        <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -1213,13 +1429,36 @@
         <v>13</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" t="s">
+        <v>179</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -1235,21 +1474,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAB49CF7-E4D4-4F06-BD88-EA9191F7BC6F}">
   <dimension ref="A1:K21"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="1" width="14.54296875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.7265625" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="17.08984375" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="51.7265625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="32.453125" collapsed="true"/>
-    <col min="6" max="7" style="1" width="9.1796875" collapsed="true"/>
+    <col min="1" max="1" customWidth="true" style="1" width="14.53125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.73046875" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="17.06640625" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="51.73046875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="32.46484375" collapsed="true"/>
+    <col min="6" max="7" style="1" width="9.19921875" collapsed="true"/>
     <col min="8" max="8" customWidth="true" style="1" width="18.0" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="1" width="29.1796875" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="1" width="52.453125" collapsed="true"/>
-    <col min="11" max="16384" style="1" width="9.1796875" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="1" width="29.19921875" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="1" width="52.46484375" collapsed="true"/>
+    <col min="11" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1275,12 +1514,12 @@
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>170</v>
+        <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -1295,12 +1534,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>170</v>
+        <v>35</v>
       </c>
       <c r="B3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -1315,12 +1554,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>170</v>
+        <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -1335,12 +1574,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>170</v>
+        <v>35</v>
       </c>
       <c r="B5" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -1355,12 +1594,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>170</v>
+        <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -1375,12 +1614,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>170</v>
+        <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -1398,12 +1637,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>170</v>
+        <v>35</v>
       </c>
       <c r="B8" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>32</v>
@@ -1421,12 +1660,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>170</v>
+        <v>35</v>
       </c>
       <c r="B9" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>32</v>
@@ -1444,12 +1683,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>170</v>
+        <v>35</v>
       </c>
       <c r="B10" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>32</v>
@@ -1467,12 +1706,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>170</v>
+        <v>35</v>
       </c>
       <c r="B11" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>32</v>
@@ -1487,12 +1726,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>170</v>
+        <v>35</v>
       </c>
       <c r="B12" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>32</v>
@@ -1507,12 +1746,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>170</v>
+        <v>35</v>
       </c>
       <c r="B13" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>32</v>
@@ -1530,12 +1769,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>170</v>
+        <v>35</v>
       </c>
       <c r="B14" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>32</v>
@@ -1553,12 +1792,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>170</v>
+        <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>32</v>
@@ -1573,12 +1812,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>170</v>
+        <v>35</v>
       </c>
       <c r="B16" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>32</v>
@@ -1596,12 +1835,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>170</v>
+        <v>35</v>
       </c>
       <c r="B17" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>32</v>
@@ -1619,12 +1858,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>170</v>
+        <v>35</v>
       </c>
       <c r="B18" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>32</v>
@@ -1639,7 +1878,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>35</v>
       </c>
@@ -1659,15 +1898,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="B20" t="s">
-        <v>87</v>
+        <v>197</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>54</v>
@@ -1679,18 +1918,18 @@
         <v>59</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="B21" t="s">
-        <v>88</v>
+        <v>198</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>54</v>
@@ -1702,7 +1941,7 @@
         <v>32</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>168</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -1716,21 +1955,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A22222EF-2A37-441E-9CE4-90FD36DC8DDC}">
   <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.1796875" collapsed="true"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
     <col min="2" max="2" customWidth="true" style="1" width="35.0" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="24.1796875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="24.453125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="24.19921875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="24.46484375" collapsed="true"/>
     <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="27.0" collapsed="true"/>
-    <col min="6" max="6" style="1" width="9.1796875" collapsed="true"/>
+    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
     <col min="7" max="7" customWidth="true" style="1" width="17.0" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="1" width="16.26953125" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="1" width="48.453125" collapsed="true"/>
-    <col min="10" max="16384" style="1" width="9.1796875" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="16.265625" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="1" width="48.46484375" collapsed="true"/>
+    <col min="10" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1756,12 +1995,12 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>170</v>
+        <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -1773,7 +2012,7 @@
         <v>8</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>22</v>
@@ -1782,12 +2021,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>170</v>
+        <v>35</v>
       </c>
       <c r="B3" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -1799,18 +2038,18 @@
         <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>170</v>
+        <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -1822,18 +2061,18 @@
         <v>10</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>170</v>
+        <v>35</v>
       </c>
       <c r="B5" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -1845,18 +2084,18 @@
         <v>11</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>170</v>
+        <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -1868,18 +2107,18 @@
         <v>12</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>170</v>
+        <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -1891,7 +2130,7 @@
         <v>13</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>32</v>
@@ -1909,23 +2148,23 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3B7105E-5E71-456F-8D2A-C4C503B29111}">
   <dimension ref="A1:L61"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.1796875" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="1" width="30.26953125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="13.26953125" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="31.7265625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="38.7265625" collapsed="true"/>
-    <col min="6" max="6" style="1" width="9.1796875" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="1" width="19.81640625" collapsed="true"/>
-    <col min="8" max="8" style="1" width="9.1796875" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="1" width="15.7265625" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="1" width="13.26953125" collapsed="true"/>
-    <col min="11" max="11" customWidth="true" style="1" width="70.7265625" collapsed="true"/>
-    <col min="12" max="16384" style="1" width="9.1796875" collapsed="true"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="1" width="30.265625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="13.265625" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="31.73046875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="38.73046875" collapsed="true"/>
+    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="1" width="19.796875" collapsed="true"/>
+    <col min="8" max="8" style="1" width="9.19921875" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="1" width="15.73046875" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="1" width="13.265625" collapsed="true"/>
+    <col min="11" max="11" customWidth="true" style="1" width="70.73046875" collapsed="true"/>
+    <col min="12" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1957,12 +2196,12 @@
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>170</v>
+        <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -1973,19 +2212,19 @@
       <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="1">
-        <v>2024</v>
+      <c r="F2" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>35</v>
       </c>
       <c r="B3" t="s">
-        <v>112</v>
+        <v>206</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -1996,19 +2235,19 @@
       <c r="E3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="1">
-        <v>2024</v>
+      <c r="F3" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>141</v>
+        <v>207</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -2019,19 +2258,19 @@
       <c r="E4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="1">
-        <v>2024</v>
+      <c r="F4" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>35</v>
       </c>
       <c r="B5" t="s">
-        <v>113</v>
+        <v>208</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -2042,19 +2281,19 @@
       <c r="E5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="1">
-        <v>2024</v>
+      <c r="F5" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>114</v>
+        <v>209</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -2065,19 +2304,19 @@
       <c r="E6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="1">
-        <v>2024</v>
+      <c r="F6" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>115</v>
+        <v>210</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -2088,19 +2327,19 @@
       <c r="E7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="1">
-        <v>2023</v>
+      <c r="F7" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>35</v>
       </c>
       <c r="B8" t="s">
-        <v>116</v>
+        <v>211</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>32</v>
@@ -2111,19 +2350,19 @@
       <c r="E8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="1">
-        <v>2023</v>
+      <c r="F8" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>35</v>
       </c>
       <c r="B9" t="s">
-        <v>117</v>
+        <v>212</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>32</v>
@@ -2134,19 +2373,19 @@
       <c r="E9" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="1">
-        <v>2023</v>
+      <c r="F9" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>35</v>
       </c>
       <c r="B10" t="s">
-        <v>142</v>
+        <v>213</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>32</v>
@@ -2157,19 +2396,19 @@
       <c r="E10" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F10" s="1">
-        <v>2023</v>
+      <c r="F10" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>35</v>
       </c>
       <c r="B11" t="s">
-        <v>118</v>
+        <v>214</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>32</v>
@@ -2180,19 +2419,19 @@
       <c r="E11" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F11" s="1">
-        <v>2023</v>
+      <c r="F11" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>35</v>
       </c>
       <c r="B12" t="s">
-        <v>119</v>
+        <v>215</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>32</v>
@@ -2203,19 +2442,19 @@
       <c r="E12" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F12" s="1">
-        <v>2022</v>
+      <c r="F12" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>35</v>
       </c>
       <c r="B13" t="s">
-        <v>143</v>
+        <v>216</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>32</v>
@@ -2226,19 +2465,19 @@
       <c r="E13" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F13" s="1">
-        <v>2022</v>
+      <c r="F13" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>35</v>
       </c>
       <c r="B14" t="s">
-        <v>120</v>
+        <v>217</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>32</v>
@@ -2249,19 +2488,19 @@
       <c r="E14" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F14" s="1">
-        <v>2022</v>
+      <c r="F14" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>121</v>
+        <v>218</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>32</v>
@@ -2272,19 +2511,19 @@
       <c r="E15" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F15" s="1">
-        <v>2022</v>
+      <c r="F15" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>35</v>
       </c>
       <c r="B16" t="s">
-        <v>144</v>
+        <v>219</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>32</v>
@@ -2295,19 +2534,19 @@
       <c r="E16" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F16" s="1">
-        <v>2022</v>
+      <c r="F16" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>35</v>
       </c>
       <c r="B17" t="s">
-        <v>145</v>
+        <v>220</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>32</v>
@@ -2319,7 +2558,7 @@
         <v>38</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>32</v>
@@ -2331,12 +2570,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>35</v>
       </c>
       <c r="B18" t="s">
-        <v>122</v>
+        <v>221</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>32</v>
@@ -2348,7 +2587,7 @@
         <v>29</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>32</v>
@@ -2360,12 +2599,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>35</v>
       </c>
       <c r="B19" t="s">
-        <v>123</v>
+        <v>222</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>32</v>
@@ -2377,7 +2616,7 @@
         <v>25</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>32</v>
@@ -2389,12 +2628,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>35</v>
       </c>
       <c r="B20" t="s">
-        <v>146</v>
+        <v>223</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>32</v>
@@ -2405,19 +2644,19 @@
       <c r="E20" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F20" s="1">
-        <v>2024</v>
+      <c r="F20" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="K20" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>35</v>
       </c>
       <c r="B21" t="s">
-        <v>147</v>
+        <v>224</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>32</v>
@@ -2429,7 +2668,7 @@
         <v>40</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>49</v>
@@ -2441,12 +2680,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>35</v>
       </c>
       <c r="B22" t="s">
-        <v>124</v>
+        <v>225</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>32</v>
@@ -2458,7 +2697,7 @@
         <v>46</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>32</v>
@@ -2470,12 +2709,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>35</v>
       </c>
       <c r="B23" t="s">
-        <v>148</v>
+        <v>226</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>32</v>
@@ -2487,7 +2726,7 @@
         <v>41</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>32</v>
@@ -2496,12 +2735,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>35</v>
       </c>
       <c r="B24" t="s">
-        <v>149</v>
+        <v>227</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>32</v>
@@ -2513,7 +2752,7 @@
         <v>27</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>32</v>
@@ -2525,12 +2764,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>35</v>
       </c>
       <c r="B25" t="s">
-        <v>125</v>
+        <v>228</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>32</v>
@@ -2542,7 +2781,7 @@
         <v>42</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>32</v>
@@ -2554,12 +2793,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>35</v>
       </c>
       <c r="B26" t="s">
-        <v>150</v>
+        <v>229</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>32</v>
@@ -2571,7 +2810,7 @@
         <v>43</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>32</v>
@@ -2583,12 +2822,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>35</v>
       </c>
       <c r="B27" t="s">
-        <v>151</v>
+        <v>230</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>32</v>
@@ -2600,7 +2839,7 @@
         <v>44</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>32</v>
@@ -2609,12 +2848,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>152</v>
+        <v>231</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>32</v>
@@ -2626,7 +2865,7 @@
         <v>28</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>32</v>
@@ -2638,12 +2877,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>153</v>
+        <v>232</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>32</v>
@@ -2654,8 +2893,8 @@
       <c r="E29" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F29" s="1">
-        <v>2024</v>
+      <c r="F29" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>32</v>
@@ -2667,12 +2906,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>154</v>
+        <v>233</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>32</v>
@@ -2683,8 +2922,8 @@
       <c r="E30" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F30" s="1">
-        <v>2024</v>
+      <c r="F30" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>32</v>
@@ -2696,12 +2935,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>35</v>
       </c>
       <c r="B31" t="s">
-        <v>155</v>
+        <v>234</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>32</v>
@@ -2712,8 +2951,8 @@
       <c r="E31" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F31" s="1">
-        <v>2024</v>
+      <c r="F31" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>32</v>
@@ -2725,12 +2964,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>35</v>
       </c>
       <c r="B32" t="s">
-        <v>126</v>
+        <v>235</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>32</v>
@@ -2741,19 +2980,19 @@
       <c r="E32" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F32" s="1">
-        <v>2023</v>
+      <c r="F32" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="K32" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>35</v>
       </c>
       <c r="B33" t="s">
-        <v>127</v>
+        <v>236</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>32</v>
@@ -2764,8 +3003,8 @@
       <c r="E33" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F33" s="1">
-        <v>2024</v>
+      <c r="F33" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>49</v>
@@ -2777,12 +3016,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>128</v>
+        <v>237</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>32</v>
@@ -2793,8 +3032,8 @@
       <c r="E34" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F34" s="1">
-        <v>2024</v>
+      <c r="F34" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>32</v>
@@ -2806,12 +3045,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>35</v>
       </c>
       <c r="B35" t="s">
-        <v>129</v>
+        <v>238</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>32</v>
@@ -2822,8 +3061,8 @@
       <c r="E35" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F35" s="1">
-        <v>2024</v>
+      <c r="F35" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>32</v>
@@ -2832,12 +3071,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>130</v>
+        <v>239</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>32</v>
@@ -2848,8 +3087,8 @@
       <c r="E36" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F36" s="1">
-        <v>2024</v>
+      <c r="F36" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>32</v>
@@ -2861,12 +3100,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>156</v>
+        <v>240</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>32</v>
@@ -2877,8 +3116,8 @@
       <c r="E37" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F37" s="1">
-        <v>2024</v>
+      <c r="F37" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>32</v>
@@ -2890,12 +3129,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>157</v>
+        <v>241</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>32</v>
@@ -2906,8 +3145,8 @@
       <c r="E38" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F38" s="1">
-        <v>2024</v>
+      <c r="F38" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>32</v>
@@ -2919,12 +3158,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>35</v>
       </c>
       <c r="B39" t="s">
-        <v>131</v>
+        <v>242</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>32</v>
@@ -2935,8 +3174,8 @@
       <c r="E39" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F39" s="1">
-        <v>2024</v>
+      <c r="F39" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>32</v>
@@ -2945,12 +3184,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>35</v>
       </c>
       <c r="B40" t="s">
-        <v>132</v>
+        <v>243</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>32</v>
@@ -2961,8 +3200,8 @@
       <c r="E40" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F40" s="1">
-        <v>2024</v>
+      <c r="F40" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>32</v>
@@ -2974,12 +3213,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>35</v>
       </c>
       <c r="B41" t="s">
-        <v>158</v>
+        <v>244</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>32</v>
@@ -2990,8 +3229,8 @@
       <c r="E41" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F41" s="1">
-        <v>2023</v>
+      <c r="F41" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="H41" s="1" t="s">
         <v>32</v>
@@ -3003,12 +3242,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>35</v>
       </c>
       <c r="B42" t="s">
-        <v>159</v>
+        <v>245</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>32</v>
@@ -3019,8 +3258,8 @@
       <c r="E42" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F42" s="1">
-        <v>2023</v>
+      <c r="F42" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>32</v>
@@ -3032,12 +3271,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>35</v>
       </c>
       <c r="B43" t="s">
-        <v>160</v>
+        <v>246</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>32</v>
@@ -3048,8 +3287,8 @@
       <c r="E43" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F43" s="1">
-        <v>2023</v>
+      <c r="F43" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>32</v>
@@ -3061,12 +3300,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>35</v>
       </c>
       <c r="B44" t="s">
-        <v>161</v>
+        <v>247</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>32</v>
@@ -3077,19 +3316,19 @@
       <c r="E44" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F44" s="1">
-        <v>2022</v>
+      <c r="F44" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="K44" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>35</v>
       </c>
       <c r="B45" t="s">
-        <v>133</v>
+        <v>248</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>32</v>
@@ -3100,8 +3339,8 @@
       <c r="E45" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F45" s="1">
-        <v>2023</v>
+      <c r="F45" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="I45" s="1" t="s">
         <v>49</v>
@@ -3113,12 +3352,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>35</v>
       </c>
       <c r="B46" t="s">
-        <v>134</v>
+        <v>249</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>32</v>
@@ -3129,8 +3368,8 @@
       <c r="E46" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F46" s="1">
-        <v>2023</v>
+      <c r="F46" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="H46" s="1" t="s">
         <v>32</v>
@@ -3142,12 +3381,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>35</v>
       </c>
       <c r="B47" t="s">
-        <v>162</v>
+        <v>250</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>32</v>
@@ -3158,8 +3397,8 @@
       <c r="E47" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F47" s="1">
-        <v>2023</v>
+      <c r="F47" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="H47" s="1" t="s">
         <v>32</v>
@@ -3168,12 +3407,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>35</v>
       </c>
       <c r="B48" t="s">
-        <v>135</v>
+        <v>251</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>32</v>
@@ -3184,8 +3423,8 @@
       <c r="E48" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F48" s="1">
-        <v>2023</v>
+      <c r="F48" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="H48" s="1" t="s">
         <v>32</v>
@@ -3197,12 +3436,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>35</v>
       </c>
       <c r="B49" t="s">
-        <v>136</v>
+        <v>252</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>32</v>
@@ -3213,8 +3452,8 @@
       <c r="E49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F49" s="1">
-        <v>2023</v>
+      <c r="F49" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>32</v>
@@ -3226,12 +3465,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>35</v>
       </c>
       <c r="B50" t="s">
-        <v>163</v>
+        <v>253</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>32</v>
@@ -3242,8 +3481,8 @@
       <c r="E50" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F50" s="1">
-        <v>2023</v>
+      <c r="F50" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>32</v>
@@ -3255,12 +3494,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>35</v>
       </c>
       <c r="B51" t="s">
-        <v>164</v>
+        <v>254</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>32</v>
@@ -3271,8 +3510,8 @@
       <c r="E51" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F51" s="1">
-        <v>2023</v>
+      <c r="F51" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>32</v>
@@ -3281,12 +3520,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>35</v>
       </c>
       <c r="B52" t="s">
-        <v>165</v>
+        <v>255</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>32</v>
@@ -3297,8 +3536,8 @@
       <c r="E52" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F52" s="1">
-        <v>2023</v>
+      <c r="F52" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="H52" s="1" t="s">
         <v>32</v>
@@ -3310,15 +3549,15 @@
         <v>60</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="B53" t="s">
-        <v>137</v>
+        <v>256</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>16</v>
@@ -3327,21 +3566,21 @@
         <v>57</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="B54" t="s">
-        <v>138</v>
+        <v>257</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>16</v>
@@ -3350,16 +3589,16 @@
         <v>58</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>32</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>35</v>
       </c>
@@ -3376,7 +3615,7 @@
         <v>45</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>32</v>
@@ -3385,15 +3624,15 @@
         <v>23</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="B56" t="s">
-        <v>166</v>
+        <v>258</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>16</v>
@@ -3402,21 +3641,21 @@
         <v>57</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="B57" t="s">
-        <v>167</v>
+        <v>259</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>16</v>
@@ -3425,16 +3664,16 @@
         <v>58</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>32</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>35</v>
       </c>
@@ -3451,7 +3690,7 @@
         <v>45</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>32</v>
@@ -3460,15 +3699,15 @@
         <v>52</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="B59" t="s">
-        <v>139</v>
+        <v>260</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>16</v>
@@ -3477,21 +3716,21 @@
         <v>57</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="B60" t="s">
-        <v>140</v>
+        <v>261</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>16</v>
@@ -3500,16 +3739,16 @@
         <v>58</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="G60" s="1" t="s">
         <v>32</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>35</v>
       </c>
@@ -3526,7 +3765,7 @@
         <v>45</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="G61" s="1" t="s">
         <v>32</v>
@@ -3548,17 +3787,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C48EC9F-E6C0-40A2-877C-8FE515BAA791}">
   <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.1796875" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="1" width="22.453125" collapsed="true"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="1" width="22.46484375" collapsed="true"/>
     <col min="3" max="3" customWidth="true" style="1" width="23.0" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="50.81640625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="46.26953125" collapsed="true"/>
-    <col min="6" max="16384" style="1" width="9.1796875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
+    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3578,7 +3817,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
@@ -3589,7 +3828,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="D3" s="1" t="s">
         <v>14</v>
       </c>
@@ -3597,7 +3836,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="C4" s="1" t="s">
         <v>36</v>
       </c>
@@ -3611,7 +3850,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="D5" s="1" t="s">
         <v>16</v>
       </c>
@@ -3622,7 +3861,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="D6" s="1" t="s">
         <v>16</v>
       </c>
@@ -3633,7 +3872,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="D7" s="1" t="s">
         <v>16</v>
       </c>
@@ -3655,17 +3894,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE13C096-3F8A-4B4D-A3EE-3415763F7F13}">
   <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.1796875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.453125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="14.453125" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="50.81640625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="46.26953125" collapsed="true"/>
-    <col min="6" max="16384" style="1" width="9.1796875" collapsed="true"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.46484375" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="14.46484375" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
+    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3685,12 +3924,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>101</v>
+        <v>263</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -3702,15 +3941,15 @@
         <v>17</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="B3" t="s">
-        <v>102</v>
+        <v>264</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -3722,15 +3961,15 @@
         <v>17</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>103</v>
+        <v>265</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -3742,15 +3981,15 @@
         <v>17</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>35</v>
       </c>
       <c r="B5" t="s">
-        <v>104</v>
+        <v>266</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -3762,15 +4001,15 @@
         <v>17</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>105</v>
+        <v>267</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -3782,10 +4021,10 @@
         <v>17</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>35</v>
       </c>
@@ -3805,7 +4044,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>35</v>
       </c>
@@ -3825,7 +4064,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>35</v>
       </c>
@@ -3853,17 +4092,17 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A156AB6-80FF-4E48-B399-7CA373BDFD42}">
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.1796875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.7265625" collapsed="true"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.73046875" collapsed="true"/>
     <col min="3" max="3" customWidth="true" style="1" width="17.0" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="50.81640625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="46.26953125" collapsed="true"/>
-    <col min="6" max="16384" style="1" width="9.1796875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
+    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3883,12 +4122,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>106</v>
+        <v>268</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -3900,15 +4139,15 @@
         <v>17</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>35</v>
       </c>
       <c r="B3" t="s">
-        <v>107</v>
+        <v>269</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -3920,15 +4159,15 @@
         <v>17</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>108</v>
+        <v>270</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -3940,15 +4179,15 @@
         <v>17</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>35</v>
       </c>
       <c r="B5" t="s">
-        <v>109</v>
+        <v>271</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -3960,15 +4199,15 @@
         <v>17</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>110</v>
+        <v>272</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -3980,7 +4219,7 @@
         <v>17</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -3991,17 +4230,17 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03F3D31C-4F04-42F4-8C54-828F1948951D}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.1796875" collapsed="true"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
     <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.0" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="15.81640625" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="50.81640625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="46.26953125" collapsed="true"/>
-    <col min="6" max="16384" style="1" width="9.1796875" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="15.796875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
+    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4018,12 +4257,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>100</v>
+        <v>262</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -4035,7 +4274,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>35</v>
       </c>

--- a/KatalonData/RADTestData/Summary.xlsx
+++ b/KatalonData/RADTestData/Summary.xlsx
@@ -1,33 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\RADTestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{134BC73E-D858-4B1B-9596-20070A3695CF}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD616801-2AD4-4DCA-8BEC-D90B192EDD91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="1" windowHeight="15675" windowWidth="28996" xWindow="-98" xr2:uid="{D99FAB39-5CE6-4AA4-B9C6-99B1EFA0654E}" yWindow="-98"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="3" xr2:uid="{D99FAB39-5CE6-4AA4-B9C6-99B1EFA0654E}"/>
   </bookViews>
   <sheets>
-    <sheet name="Estimated" r:id="rId1" sheetId="1"/>
-    <sheet name="Existing" r:id="rId2" sheetId="2"/>
-    <sheet name="Extension" r:id="rId3" sheetId="3"/>
-    <sheet name="NewTaxReturn" r:id="rId4" sheetId="4"/>
-    <sheet name="Personal" r:id="rId5" sheetId="5"/>
-    <sheet name="Personal_IND" r:id="rId6" sheetId="6"/>
-    <sheet name="Personal_JNT" r:id="rId7" sheetId="7"/>
-    <sheet name="Personal_EL" r:id="rId8" sheetId="8"/>
+    <sheet name="Estimated" sheetId="1" r:id="rId1"/>
+    <sheet name="Existing" sheetId="2" r:id="rId2"/>
+    <sheet name="Extension" sheetId="3" r:id="rId3"/>
+    <sheet name="NewTaxReturn" sheetId="4" r:id="rId4"/>
+    <sheet name="Personal" sheetId="5" r:id="rId5"/>
+    <sheet name="Personal_IND" sheetId="6" r:id="rId6"/>
+    <sheet name="Personal_JNT" sheetId="7" r:id="rId7"/>
+    <sheet name="Personal_EL" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="3" name="_xlnm._FilterDatabase">NewTaxReturn!$E$1:$E$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">NewTaxReturn!$E$1:$E$52</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1277" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="886" uniqueCount="169">
   <si>
     <t>Result</t>
   </si>
@@ -231,18 +231,6 @@
     <t>Federal EIN is not present, Wrong App ID in QA</t>
   </si>
   <si>
-    <t>Mon Feb 24 18:22:50 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 19:02:37 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 19:04:23 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 19:06:09 EST 2025</t>
-  </si>
-  <si>
     <t>Mon Feb 24 19:07:24 EST 2025</t>
   </si>
   <si>
@@ -255,623 +243,322 @@
     <t>Mon Feb 24 19:11:54 EST 2025</t>
   </si>
   <si>
-    <t>Tue Nov 04 18:35:13 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 20:28:06 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 20:30:16 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:12:56 EST 2025</t>
-  </si>
-  <si>
     <t>This is in QA and Demo but not in Production</t>
   </si>
   <si>
     <t>2026</t>
   </si>
   <si>
+    <t>Thu Jun 25 00:14:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:14:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:15:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:15:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:16:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:21:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:21:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:21:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:22:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:22:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:22:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:22:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:23:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:23:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:23:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:23:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:23:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:24:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:24:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:24:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:24:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:24:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:25:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:29:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:29:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:29:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:30:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:30:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:30:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:30:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:31:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:31:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:31:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:31:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:32:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:32:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:32:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:33:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:33:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:33:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:34:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:34:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:34:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:35:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:35:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:35:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:36:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:36:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:37:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:37:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:37:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:37:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:38:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:38:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:38:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:39:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:39:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:39:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:40:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:40:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:41:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:41:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:41:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:42:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:42:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:42:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:42:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:43:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:43:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:43:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:44:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:44:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:45:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:45:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:46:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:46:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:46:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:48:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:48:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:48:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:48:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:49:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:49:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:49:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:49:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:50:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:50:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:51:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:51:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 15:01:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 15:02:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>MFInsNum</t>
+  </si>
+  <si>
+    <t>Motor Fuel Floor Tax</t>
+  </si>
+  <si>
     <t>Fail</t>
   </si>
   <si>
-    <t>Thu May 28 17:38:55 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:39:22 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:39:37 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:39:52 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:40:10 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:40:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:40:49 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:41:07 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:41:21 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:41:35 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:41:49 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:42:02 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:42:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:42:37 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:42:52 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:43:05 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:43:19 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:43:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:43:46 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:44:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:44:16 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:44:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:44:46 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:44:58 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:45:15 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:45:29 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:45:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:45:56 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:46:11 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:46:30 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:46:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:47:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:47:20 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:47:40 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:48:01 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:48:27 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:48:47 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:49:06 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:49:27 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:49:46 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:50:07 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:50:30 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:50:52 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:51:11 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:51:31 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:51:51 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:52:12 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:52:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:52:52 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:53:12 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:53:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:53:54 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:54:17 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:54:36 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:54:56 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:55:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:55:37 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:56:01 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:56:21 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:56:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:57:06 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:57:28 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:57:50 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:58:12 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:58:31 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:58:51 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:59:11 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:59:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 17:59:52 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 18:00:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 18:00:43 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 18:01:06 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 18:01:27 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 18:01:47 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 18:02:08 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 18:02:29 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 18:02:49 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 18:03:13 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 18:03:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 18:03:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 18:04:13 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 18:04:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 18:04:54 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 18:05:19 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 18:05:38 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 18:05:58 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 18:06:34 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 18:06:52 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 18:07:04 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 18:07:39 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 18:07:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 18:08:20 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 18:08:45 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 18:09:13 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 18:09:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 18:10:09 EDT 2026</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Fri May 29 16:50:29 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 16:51:23 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 16:52:17 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 16:53:10 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 16:54:02 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 16:54:55 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 16:55:48 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 16:56:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 16:57:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 16:58:24 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 16:59:14 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:00:09 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:01:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:01:52 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:02:43 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:03:36 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:04:27 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:05:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:06:09 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:07:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:07:52 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:08:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:09:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:10:25 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:11:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:12:09 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:12:59 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:13:50 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:14:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:15:31 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:16:21 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:17:13 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:18:04 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:19:01 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:19:58 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:20:56 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:21:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:22:50 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:23:47 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:24:45 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:25:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:26:39 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:27:35 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:28:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:29:29 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:30:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:31:28 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:32:25 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:33:23 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:34:19 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:35:17 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:36:13 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:37:10 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:38:09 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:39:07 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:40:06 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:41:03 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:41:59 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:42:57 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:43:54 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:44:51 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:45:47 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:46:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:47:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:48:38 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:49:36 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:50:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:51:30 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:52:29 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:53:26 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:54:23 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:55:19 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:56:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:57:15 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:58:13 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 17:59:11 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 18:00:16 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 18:01:15 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 18:02:11 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 18:03:08 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 18:04:06 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 18:05:03 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 18:06:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 18:06:57 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 18:07:55 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 18:08:52 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 18:09:48 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 18:10:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 18:11:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 18:12:37 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 18:13:31 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 18:14:22 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 18:15:43 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 18:16:37 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 18:17:46 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 18:18:38 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 18:19:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 18:20:45 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 18:21:47 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 18:22:51 EDT 2026</t>
+    <t>Thu Jul 09 14:23:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 14:23:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 14:23:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 14:23:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 14:24:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 14:24:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 14:25:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 15:06:39 EDT 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -920,19 +607,19 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -949,10 +636,10 @@
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -987,7 +674,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
-        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -1039,7 +726,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1150,21 +837,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -1181,7 +868,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -1233,27 +920,27 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office 2013 - 2022 Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19BDCA51-7A9D-4BB2-A660-F3BEEC814D67}">
-  <dimension ref="A1:J8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19BDCA51-7A9D-4BB2-A660-F3BEEC814D67}">
+  <dimension ref="A1:I8"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.73046875" collapsed="true"/>
-    <col min="3" max="3" style="1" width="9.19921875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="44.53125" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="35.53125" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="1" width="15.265625" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="1" width="17.265625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="1" width="19.53125" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="1" width="40.19921875" collapsed="true"/>
-    <col min="10" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="26.73046875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="9.19921875" style="1" collapsed="1"/>
+    <col min="4" max="4" width="44.53125" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="35.53125" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="15.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="17.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="19.53125" style="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="40.19921875" style="1" customWidth="1" collapsed="1"/>
+    <col min="10" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
@@ -1283,11 +970,11 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B2" t="s">
-        <v>173</v>
+      <c r="A2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -1299,7 +986,7 @@
         <v>8</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>19</v>
@@ -1309,11 +996,11 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B3" t="s">
-        <v>174</v>
+      <c r="A3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -1325,7 +1012,7 @@
         <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>20</v>
@@ -1335,11 +1022,11 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B4" t="s">
-        <v>175</v>
+      <c r="A4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>156</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -1351,7 +1038,7 @@
         <v>10</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>21</v>
@@ -1361,11 +1048,11 @@
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" t="s">
-        <v>176</v>
+      <c r="A5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>69</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -1377,7 +1064,7 @@
         <v>11</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>22</v>
@@ -1387,11 +1074,11 @@
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" t="s">
-        <v>177</v>
+      <c r="A6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>70</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -1403,7 +1090,7 @@
         <v>12</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>23</v>
@@ -1413,11 +1100,11 @@
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" t="s">
-        <v>178</v>
+      <c r="A7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>157</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -1429,7 +1116,7 @@
         <v>13</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>24</v>
@@ -1439,11 +1126,11 @@
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>75</v>
-      </c>
-      <c r="B8" t="s">
-        <v>179</v>
+      <c r="A8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>71</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>32</v>
@@ -1455,7 +1142,7 @@
         <v>57</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>53</v>
@@ -1463,8 +1150,8 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup horizontalDpi="4294967293" orientation="portrait" r:id="rId1" verticalDpi="0"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
@@ -1472,20 +1159,20 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAB49CF7-E4D4-4F06-BD88-EA9191F7BC6F}">
-  <dimension ref="A1:K21"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAB49CF7-E4D4-4F06-BD88-EA9191F7BC6F}">
+  <dimension ref="A1:J21"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="1" width="14.53125" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.73046875" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="17.06640625" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="51.73046875" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="32.46484375" collapsed="true"/>
-    <col min="6" max="7" style="1" width="9.19921875" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="1" width="18.0" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="1" width="29.19921875" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="1" width="52.46484375" collapsed="true"/>
-    <col min="11" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="14.53125" style="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="26.73046875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="17.06640625" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="51.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="32.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="7" width="9.19921875" style="1" collapsed="1"/>
+    <col min="8" max="8" width="18" style="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="29.19921875" style="1" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="52.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="11" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
@@ -1515,11 +1202,11 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B2" t="s">
-        <v>180</v>
+      <c r="A2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>72</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -1535,11 +1222,11 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B3" t="s">
-        <v>181</v>
+      <c r="A3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>73</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -1555,11 +1242,11 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B4" t="s">
-        <v>182</v>
+      <c r="A4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>74</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -1575,11 +1262,11 @@
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" t="s">
-        <v>183</v>
+      <c r="A5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>75</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -1595,11 +1282,11 @@
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" t="s">
-        <v>184</v>
+      <c r="A6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>76</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -1615,11 +1302,11 @@
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" t="s">
-        <v>185</v>
+      <c r="A7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>77</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -1638,11 +1325,11 @@
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" t="s">
-        <v>186</v>
+      <c r="A8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>78</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>32</v>
@@ -1661,11 +1348,11 @@
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" t="s">
-        <v>187</v>
+      <c r="A9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>79</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>32</v>
@@ -1684,11 +1371,11 @@
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>35</v>
-      </c>
-      <c r="B10" t="s">
-        <v>188</v>
+      <c r="A10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>80</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>32</v>
@@ -1707,11 +1394,11 @@
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>35</v>
-      </c>
-      <c r="B11" t="s">
-        <v>189</v>
+      <c r="A11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>81</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>32</v>
@@ -1727,11 +1414,11 @@
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>35</v>
-      </c>
-      <c r="B12" t="s">
-        <v>190</v>
+      <c r="A12" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>82</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>32</v>
@@ -1747,11 +1434,11 @@
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" t="s">
-        <v>191</v>
+      <c r="A13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>32</v>
@@ -1770,11 +1457,11 @@
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14" t="s">
-        <v>192</v>
+      <c r="A14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>32</v>
@@ -1793,11 +1480,11 @@
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" t="s">
-        <v>193</v>
+      <c r="A15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>85</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>32</v>
@@ -1813,11 +1500,11 @@
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16" t="s">
-        <v>194</v>
+      <c r="A16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>86</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>32</v>
@@ -1836,11 +1523,11 @@
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
-        <v>35</v>
-      </c>
-      <c r="B17" t="s">
-        <v>195</v>
+      <c r="A17" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>87</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>32</v>
@@ -1859,11 +1546,11 @@
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
-        <v>35</v>
-      </c>
-      <c r="B18" t="s">
-        <v>196</v>
+      <c r="A18" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>32</v>
@@ -1879,12 +1566,6 @@
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A19" t="s">
-        <v>35</v>
-      </c>
-      <c r="B19" t="s">
-        <v>61</v>
-      </c>
       <c r="C19" s="1" t="s">
         <v>36</v>
       </c>
@@ -1899,11 +1580,11 @@
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A20" t="s">
-        <v>75</v>
-      </c>
-      <c r="B20" t="s">
-        <v>197</v>
+      <c r="A20" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>32</v>
@@ -1918,18 +1599,12 @@
         <v>59</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A21" t="s">
-        <v>75</v>
-      </c>
-      <c r="B21" t="s">
-        <v>198</v>
-      </c>
       <c r="C21" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>54</v>
@@ -1941,11 +1616,11 @@
         <v>32</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
@@ -1953,20 +1628,20 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A22222EF-2A37-441E-9CE4-90FD36DC8DDC}">
-  <dimension ref="A1:J7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A22222EF-2A37-441E-9CE4-90FD36DC8DDC}">
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="1" width="35.0" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="24.19921875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="24.46484375" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="27.0" collapsed="true"/>
-    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="1" width="17.0" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="1" width="16.265625" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="1" width="48.46484375" collapsed="true"/>
-    <col min="10" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="35" style="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="24.19921875" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="24.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="27" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
+    <col min="7" max="7" width="17" style="1" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="16.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="48.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="10" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
@@ -1996,11 +1671,11 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B2" t="s">
-        <v>199</v>
+      <c r="A2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>90</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -2022,11 +1697,11 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B3" t="s">
-        <v>200</v>
+      <c r="A3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -2045,11 +1720,11 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B4" t="s">
-        <v>201</v>
+      <c r="A4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -2068,11 +1743,11 @@
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" t="s">
-        <v>202</v>
+      <c r="A5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>93</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -2091,11 +1766,11 @@
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" t="s">
-        <v>203</v>
+      <c r="A6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>94</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -2114,11 +1789,11 @@
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" t="s">
-        <v>204</v>
+      <c r="A7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -2138,7 +1813,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
@@ -2146,25 +1821,26 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3B7105E-5E71-456F-8D2A-C4C503B29111}">
-  <dimension ref="A1:L61"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3B7105E-5E71-456F-8D2A-C4C503B29111}">
+  <dimension ref="A1:L64"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="1" width="30.265625" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="13.265625" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="31.73046875" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="38.73046875" collapsed="true"/>
-    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="1" width="19.796875" collapsed="true"/>
-    <col min="8" max="8" style="1" width="9.19921875" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="1" width="15.73046875" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="1" width="13.265625" collapsed="true"/>
-    <col min="11" max="11" customWidth="true" style="1" width="70.73046875" collapsed="true"/>
-    <col min="12" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="30.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="13.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="31.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="38.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
+    <col min="7" max="7" width="19.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="9.19921875" style="1" collapsed="1"/>
+    <col min="9" max="9" width="15.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="13.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="13.265625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="70.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="13" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2195,13 +1871,16 @@
       <c r="J1" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B2" t="s">
-        <v>205</v>
+      <c r="K1" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>96</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -2215,16 +1894,16 @@
       <c r="F2" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B3" t="s">
-        <v>206</v>
+      <c r="L2" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>97</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -2242,12 +1921,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B4" t="s">
-        <v>207</v>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>98</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -2265,12 +1944,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" t="s">
-        <v>208</v>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>99</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -2288,12 +1967,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" t="s">
-        <v>209</v>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -2311,12 +1990,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" t="s">
-        <v>210</v>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>101</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -2330,16 +2009,16 @@
       <c r="F7" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="K7" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" t="s">
-        <v>211</v>
+      <c r="L7" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>102</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>32</v>
@@ -2357,12 +2036,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" t="s">
-        <v>212</v>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>103</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>32</v>
@@ -2380,12 +2059,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>35</v>
-      </c>
-      <c r="B10" t="s">
-        <v>213</v>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>104</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>32</v>
@@ -2403,12 +2082,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>35</v>
-      </c>
-      <c r="B11" t="s">
-        <v>214</v>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>105</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>32</v>
@@ -2426,12 +2105,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>35</v>
-      </c>
-      <c r="B12" t="s">
-        <v>215</v>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A12" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>32</v>
@@ -2445,16 +2124,16 @@
       <c r="F12" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="K12" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" t="s">
-        <v>216</v>
+      <c r="L12" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>32</v>
@@ -2472,12 +2151,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14" t="s">
-        <v>217</v>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>108</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>32</v>
@@ -2495,12 +2174,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" t="s">
-        <v>218</v>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>32</v>
@@ -2518,12 +2197,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16" t="s">
-        <v>219</v>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>110</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>32</v>
@@ -2541,12 +2220,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
-        <v>35</v>
-      </c>
-      <c r="B17" t="s">
-        <v>220</v>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A17" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>111</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>32</v>
@@ -2558,7 +2237,7 @@
         <v>38</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>32</v>
@@ -2566,16 +2245,16 @@
       <c r="I17" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="K17" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
-        <v>35</v>
-      </c>
-      <c r="B18" t="s">
-        <v>221</v>
+      <c r="L17" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A18" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>112</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>32</v>
@@ -2587,7 +2266,7 @@
         <v>29</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>32</v>
@@ -2595,16 +2274,16 @@
       <c r="I18" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="K18" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A19" t="s">
-        <v>35</v>
-      </c>
-      <c r="B19" t="s">
-        <v>222</v>
+      <c r="L18" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A19" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>32</v>
@@ -2616,7 +2295,7 @@
         <v>25</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>32</v>
@@ -2624,16 +2303,16 @@
       <c r="I19" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K19" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A20" t="s">
-        <v>35</v>
-      </c>
-      <c r="B20" t="s">
-        <v>223</v>
+      <c r="L19" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A20" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>114</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>32</v>
@@ -2647,16 +2326,16 @@
       <c r="F20" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="K20" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A21" t="s">
-        <v>35</v>
-      </c>
-      <c r="B21" t="s">
-        <v>224</v>
+      <c r="L20" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A21" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>168</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>32</v>
@@ -2668,7 +2347,7 @@
         <v>40</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>49</v>
@@ -2676,16 +2355,16 @@
       <c r="J21" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K21" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A22" t="s">
-        <v>35</v>
-      </c>
-      <c r="B22" t="s">
-        <v>225</v>
+      <c r="L21" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A22" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>115</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>32</v>
@@ -2697,7 +2376,7 @@
         <v>46</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>32</v>
@@ -2705,16 +2384,16 @@
       <c r="I22" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="K22" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A23" t="s">
-        <v>35</v>
-      </c>
-      <c r="B23" t="s">
-        <v>226</v>
+      <c r="L22" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A23" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>116</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>32</v>
@@ -2726,21 +2405,21 @@
         <v>41</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K23" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A24" t="s">
-        <v>35</v>
-      </c>
-      <c r="B24" t="s">
-        <v>227</v>
+      <c r="L23" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A24" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>117</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>32</v>
@@ -2752,7 +2431,7 @@
         <v>27</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>32</v>
@@ -2760,16 +2439,16 @@
       <c r="I24" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="K24" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A25" t="s">
-        <v>35</v>
-      </c>
-      <c r="B25" t="s">
-        <v>228</v>
+      <c r="L24" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A25" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>32</v>
@@ -2781,7 +2460,7 @@
         <v>42</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>32</v>
@@ -2793,12 +2472,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A26" t="s">
-        <v>35</v>
-      </c>
-      <c r="B26" t="s">
-        <v>229</v>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A26" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>119</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>32</v>
@@ -2810,7 +2489,7 @@
         <v>43</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>32</v>
@@ -2818,16 +2497,16 @@
       <c r="I26" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="K26" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A27" t="s">
-        <v>35</v>
-      </c>
-      <c r="B27" t="s">
-        <v>230</v>
+      <c r="L26" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A27" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>120</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>32</v>
@@ -2839,7 +2518,7 @@
         <v>44</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>32</v>
@@ -2848,12 +2527,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A28" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" t="s">
-        <v>231</v>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>121</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>32</v>
@@ -2865,7 +2544,7 @@
         <v>28</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>32</v>
@@ -2873,16 +2552,16 @@
       <c r="I28" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="K28" s="1" t="s">
+      <c r="L28" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A29" t="s">
-        <v>35</v>
-      </c>
-      <c r="B29" t="s">
-        <v>232</v>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>122</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>32</v>
@@ -2902,16 +2581,16 @@
       <c r="I29" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="K29" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A30" t="s">
-        <v>35</v>
-      </c>
-      <c r="B30" t="s">
-        <v>233</v>
+      <c r="L29" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A30" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>123</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>32</v>
@@ -2931,16 +2610,16 @@
       <c r="I30" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="K30" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A31" t="s">
-        <v>35</v>
-      </c>
-      <c r="B31" t="s">
-        <v>234</v>
+      <c r="L30" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A31" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>124</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>32</v>
@@ -2960,16 +2639,16 @@
       <c r="I31" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K31" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A32" t="s">
-        <v>35</v>
-      </c>
-      <c r="B32" t="s">
-        <v>235</v>
+      <c r="L31" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A32" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>125</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>32</v>
@@ -2983,16 +2662,16 @@
       <c r="F32" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="K32" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A33" t="s">
-        <v>35</v>
-      </c>
-      <c r="B33" t="s">
-        <v>236</v>
+      <c r="L32" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A33" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>161</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>32</v>
@@ -3012,16 +2691,16 @@
       <c r="J33" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K33" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A34" t="s">
-        <v>35</v>
-      </c>
-      <c r="B34" t="s">
-        <v>237</v>
+      <c r="L33" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A34" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>126</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>32</v>
@@ -3041,16 +2720,16 @@
       <c r="I34" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="K34" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A35" t="s">
-        <v>35</v>
-      </c>
-      <c r="B35" t="s">
-        <v>238</v>
+      <c r="L34" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A35" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>32</v>
@@ -3067,16 +2746,16 @@
       <c r="H35" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K35" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A36" t="s">
-        <v>35</v>
-      </c>
-      <c r="B36" t="s">
-        <v>239</v>
+      <c r="L35" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A36" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>128</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>32</v>
@@ -3096,16 +2775,16 @@
       <c r="I36" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="K36" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A37" t="s">
-        <v>35</v>
-      </c>
-      <c r="B37" t="s">
-        <v>240</v>
+      <c r="L36" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A37" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>129</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>32</v>
@@ -3129,12 +2808,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A38" t="s">
-        <v>35</v>
-      </c>
-      <c r="B38" t="s">
-        <v>241</v>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A38" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>130</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>32</v>
@@ -3154,16 +2833,16 @@
       <c r="I38" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="K38" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A39" t="s">
-        <v>35</v>
-      </c>
-      <c r="B39" t="s">
-        <v>242</v>
+      <c r="L38" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A39" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>131</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>32</v>
@@ -3184,12 +2863,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A40" t="s">
-        <v>35</v>
-      </c>
-      <c r="B40" t="s">
-        <v>243</v>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A40" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>132</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>32</v>
@@ -3209,16 +2888,16 @@
       <c r="I40" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="K40" s="1" t="s">
+      <c r="L40" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A41" t="s">
-        <v>35</v>
-      </c>
-      <c r="B41" t="s">
-        <v>244</v>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A41" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>133</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>32</v>
@@ -3238,16 +2917,16 @@
       <c r="I41" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="K41" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A42" t="s">
-        <v>35</v>
-      </c>
-      <c r="B42" t="s">
-        <v>245</v>
+      <c r="L41" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A42" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>134</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>32</v>
@@ -3267,16 +2946,16 @@
       <c r="I42" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="K42" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A43" t="s">
-        <v>35</v>
-      </c>
-      <c r="B43" t="s">
-        <v>246</v>
+      <c r="L42" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A43" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>135</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>32</v>
@@ -3296,16 +2975,16 @@
       <c r="I43" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K43" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A44" t="s">
-        <v>35</v>
-      </c>
-      <c r="B44" t="s">
-        <v>247</v>
+      <c r="L43" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A44" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>136</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>32</v>
@@ -3319,16 +2998,16 @@
       <c r="F44" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="K44" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A45" t="s">
-        <v>35</v>
-      </c>
-      <c r="B45" t="s">
-        <v>248</v>
+      <c r="L44" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A45" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>162</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>32</v>
@@ -3348,16 +3027,16 @@
       <c r="J45" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K45" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A46" t="s">
-        <v>35</v>
-      </c>
-      <c r="B46" t="s">
-        <v>249</v>
+      <c r="L45" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A46" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>137</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>32</v>
@@ -3377,16 +3056,16 @@
       <c r="I46" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="K46" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A47" t="s">
-        <v>35</v>
-      </c>
-      <c r="B47" t="s">
-        <v>250</v>
+      <c r="L46" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A47" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>138</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>32</v>
@@ -3403,16 +3082,16 @@
       <c r="H47" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K47" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A48" t="s">
-        <v>35</v>
-      </c>
-      <c r="B48" t="s">
-        <v>251</v>
+      <c r="L47" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A48" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>163</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>32</v>
@@ -3432,16 +3111,16 @@
       <c r="I48" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="K48" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A49" t="s">
-        <v>35</v>
-      </c>
-      <c r="B49" t="s">
-        <v>252</v>
+      <c r="L48" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A49" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>139</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>32</v>
@@ -3465,12 +3144,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A50" t="s">
-        <v>35</v>
-      </c>
-      <c r="B50" t="s">
-        <v>253</v>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A50" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>140</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>32</v>
@@ -3490,16 +3169,16 @@
       <c r="I50" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="K50" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A51" t="s">
-        <v>35</v>
-      </c>
-      <c r="B51" t="s">
-        <v>254</v>
+      <c r="L50" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A51" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>141</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>32</v>
@@ -3520,12 +3199,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A52" t="s">
-        <v>35</v>
-      </c>
-      <c r="B52" t="s">
-        <v>255</v>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A52" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>142</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>32</v>
@@ -3545,16 +3224,16 @@
       <c r="I52" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="K52" s="1" t="s">
+      <c r="L52" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A53" t="s">
-        <v>75</v>
-      </c>
-      <c r="B53" t="s">
-        <v>256</v>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A53" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>143</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>32</v>
@@ -3566,21 +3245,15 @@
         <v>57</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="K53" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A54" t="s">
-        <v>75</v>
-      </c>
-      <c r="B54" t="s">
-        <v>257</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="L53" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.45">
       <c r="C54" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>16</v>
@@ -3589,22 +3262,16 @@
         <v>58</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K54" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A55" t="s">
-        <v>35</v>
-      </c>
-      <c r="B55" t="s">
-        <v>62</v>
-      </c>
+      <c r="L54" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.45">
       <c r="C55" s="1" t="s">
         <v>36</v>
       </c>
@@ -3615,7 +3282,7 @@
         <v>45</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>32</v>
@@ -3624,12 +3291,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A56" t="s">
-        <v>75</v>
-      </c>
-      <c r="B56" t="s">
-        <v>258</v>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A56" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>164</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>32</v>
@@ -3643,19 +3310,13 @@
       <c r="F56" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="K56" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A57" t="s">
-        <v>75</v>
-      </c>
-      <c r="B57" t="s">
-        <v>259</v>
-      </c>
+      <c r="L56" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.45">
       <c r="C57" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>16</v>
@@ -3669,17 +3330,11 @@
       <c r="G57" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K57" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A58" t="s">
-        <v>35</v>
-      </c>
-      <c r="B58" t="s">
-        <v>63</v>
-      </c>
+      <c r="L57" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.45">
       <c r="C58" s="1" t="s">
         <v>36</v>
       </c>
@@ -3699,12 +3354,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A59" t="s">
-        <v>75</v>
-      </c>
-      <c r="B59" t="s">
-        <v>260</v>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A59" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>144</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>32</v>
@@ -3718,19 +3373,13 @@
       <c r="F59" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="K59" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A60" t="s">
-        <v>75</v>
-      </c>
-      <c r="B60" t="s">
-        <v>261</v>
-      </c>
+      <c r="L59" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.45">
       <c r="C60" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>16</v>
@@ -3744,17 +3393,11 @@
       <c r="G60" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K60" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A61" t="s">
-        <v>35</v>
-      </c>
-      <c r="B61" t="s">
-        <v>64</v>
-      </c>
+      <c r="L60" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.45">
       <c r="C61" s="1" t="s">
         <v>36</v>
       </c>
@@ -3774,10 +3417,88 @@
         <v>51</v>
       </c>
     </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A62" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I62" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K62" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A63" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K63" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A64" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K64" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="E1:E52" xr:uid="{E3B7105E-5E71-456F-8D2A-C4C503B29111}"/>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup horizontalDpi="4294967293" orientation="portrait" r:id="rId1" verticalDpi="0"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
@@ -3785,16 +3506,16 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C48EC9F-E6C0-40A2-877C-8FE515BAA791}">
-  <dimension ref="A1:G7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C48EC9F-E6C0-40A2-877C-8FE515BAA791}">
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="1" width="22.46484375" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="23.0" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
-    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="22.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="23" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
@@ -3884,7 +3605,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
@@ -3892,16 +3613,16 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE13C096-3F8A-4B4D-A3EE-3415763F7F13}">
-  <dimension ref="A1:G9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE13C096-3F8A-4B4D-A3EE-3415763F7F13}">
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.46484375" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="14.46484375" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
-    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="26.46484375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="14.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
@@ -3925,11 +3646,11 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B2" t="s">
-        <v>263</v>
+      <c r="A2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>146</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -3941,15 +3662,15 @@
         <v>17</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>75</v>
-      </c>
-      <c r="B3" t="s">
-        <v>264</v>
+      <c r="A3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>147</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -3965,11 +3686,11 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B4" t="s">
-        <v>265</v>
+      <c r="A4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>148</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -3985,11 +3706,11 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" t="s">
-        <v>266</v>
+      <c r="A5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>149</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -4005,11 +3726,11 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" t="s">
-        <v>267</v>
+      <c r="A6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>150</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -4025,11 +3746,11 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" t="s">
-        <v>66</v>
+      <c r="A7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>62</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>36</v>
@@ -4045,11 +3766,11 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" t="s">
-        <v>67</v>
+      <c r="A8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>36</v>
@@ -4065,11 +3786,11 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" t="s">
-        <v>68</v>
+      <c r="A9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>36</v>
@@ -4085,21 +3806,21 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A156AB6-80FF-4E48-B399-7CA373BDFD42}">
-  <dimension ref="A1:G6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A156AB6-80FF-4E48-B399-7CA373BDFD42}">
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.73046875" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="17.0" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
-    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="27.73046875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="17" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
@@ -4123,11 +3844,11 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B2" t="s">
-        <v>268</v>
+      <c r="A2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>151</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -4139,15 +3860,15 @@
         <v>17</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B3" t="s">
-        <v>269</v>
+      <c r="A3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>152</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -4163,11 +3884,11 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B4" t="s">
-        <v>270</v>
+      <c r="A4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>153</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -4183,11 +3904,11 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" t="s">
-        <v>271</v>
+      <c r="A5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>154</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -4203,11 +3924,11 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" t="s">
-        <v>272</v>
+      <c r="A6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>155</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -4223,21 +3944,21 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03F3D31C-4F04-42F4-8C54-828F1948951D}">
-  <dimension ref="A1:F3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03F3D31C-4F04-42F4-8C54-828F1948951D}">
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.0" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="15.796875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
-    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="26" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="15.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
@@ -4258,11 +3979,11 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B2" t="s">
-        <v>262</v>
+      <c r="A2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>145</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -4275,11 +3996,11 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B3" t="s">
-        <v>65</v>
+      <c r="A3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>36</v>
@@ -4292,6 +4013,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/KatalonData/RADTestData/Summary.xlsx
+++ b/KatalonData/RADTestData/Summary.xlsx
@@ -3,14 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\RADTestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD616801-2AD4-4DCA-8BEC-D90B192EDD91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFAEFF54-5F6C-438D-AA3E-93352391360D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="3" xr2:uid="{D99FAB39-5CE6-4AA4-B9C6-99B1EFA0654E}"/>
+    <workbookView xWindow="3075" yWindow="3405" windowWidth="21600" windowHeight="11325" activeTab="5" xr2:uid="{D99FAB39-5CE6-4AA4-B9C6-99B1EFA0654E}"/>
   </bookViews>
   <sheets>
     <sheet name="Estimated" sheetId="1" r:id="rId1"/>
@@ -23,11 +23,11 @@
     <sheet name="Personal_EL" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">NewTaxReturn!$E$1:$E$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">NewTaxReturn!$E$1:$E$64</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="886" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1946" uniqueCount="699">
   <si>
     <t>Result</t>
   </si>
@@ -234,15 +234,6 @@
     <t>Mon Feb 24 19:07:24 EST 2025</t>
   </si>
   <si>
-    <t>Mon Feb 24 19:10:47 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 19:11:21 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 19:11:54 EST 2025</t>
-  </si>
-  <si>
     <t>This is in QA and Demo but not in Production</t>
   </si>
   <si>
@@ -339,18 +330,6 @@
     <t>Thu Jun 25 00:30:43 EDT 2026</t>
   </si>
   <si>
-    <t>Thu Jun 25 00:31:01 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:31:20 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:31:37 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:31:56 EDT 2026</t>
-  </si>
-  <si>
     <t>Thu Jun 25 00:32:14 EDT 2026</t>
   </si>
   <si>
@@ -402,15 +381,9 @@
     <t>Thu Jun 25 00:37:39 EDT 2026</t>
   </si>
   <si>
-    <t>Thu Jun 25 00:37:58 EDT 2026</t>
-  </si>
-  <si>
     <t>Thu Jun 25 00:38:16 EDT 2026</t>
   </si>
   <si>
-    <t>Thu Jun 25 00:38:34 EDT 2026</t>
-  </si>
-  <si>
     <t>Thu Jun 25 00:38:53 EDT 2026</t>
   </si>
   <si>
@@ -553,12 +526,1630 @@
   </si>
   <si>
     <t>Thu Jul 09 15:06:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 02 13:00:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 02 13:00:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 02 14:37:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 02 14:37:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 02 14:37:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 02 14:38:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 02 14:38:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 02 14:39:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 02 14:39:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 02 21:14:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 02 21:14:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 02 21:14:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:28:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:29:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:29:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:29:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:30:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:30:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:31:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:31:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:32:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:33:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:34:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:34:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:34:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:35:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:35:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:36:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:36:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:36:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:37:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:37:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:37:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:38:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:38:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:39:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:39:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:39:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:39:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:40:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:40:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:41:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:41:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:42:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:42:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:43:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:43:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:44:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:45:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:45:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:46:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:46:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:46:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:47:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:47:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:48:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:48:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:49:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:49:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:50:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:50:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:50:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:51:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:51:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:51:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:51:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:52:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:52:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:52:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:53:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:53:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:54:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:55:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:55:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:56:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:56:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:56:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:57:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:57:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:58:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:58:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:58:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:59:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:59:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 21:59:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:00:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:00:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:00:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:00:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:01:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:01:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:02:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:02:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:02:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:02:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:03:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:03:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:03:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:03:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:04:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:04:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:04:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:05:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:06:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:06:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:07:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:07:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:08:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:08:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:08:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:08:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:09:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:09:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:09:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:10:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:10:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:11:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:11:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:11:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:12:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:13:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:13:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:13:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:14:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:14:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:15:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:15:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:15:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:16:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:16:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:17:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:17:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:17:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:18:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:18:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:19:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:20:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:20:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:21:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:21:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:21:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:22:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:22:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:22:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:23:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:23:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:23:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:24:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:24:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:24:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:25:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:25:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:25:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:26:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:26:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:26:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:27:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:27:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:27:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:28:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:29:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:29:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:30:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:31:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:31:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:32:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:33:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:33:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:33:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:34:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:34:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:35:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:35:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:35:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:36:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:36:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:37:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:37:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:37:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:38:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:38:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:38:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:39:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:39:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:39:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:40:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:40:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:40:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:41:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:41:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:41:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:42:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:42:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:42:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:43:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:43:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:44:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:44:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:44:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:45:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:45:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:45:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:46:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:46:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:46:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:47:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:47:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:47:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:48:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:48:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:48:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:49:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:49:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:50:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:50:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:50:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:51:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:51:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:51:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:52:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:52:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:53:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:53:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:53:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:54:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:54:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:54:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:55:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:55:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:55:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:56:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:56:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:56:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:57:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:57:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:57:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:58:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:59:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:59:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 22:59:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:00:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:00:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:00:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:01:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:01:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:02:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:02:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:02:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:03:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:03:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:03:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:04:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:04:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:04:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:05:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:06:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:06:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:06:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:07:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:07:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:07:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:08:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:08:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:08:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:09:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:09:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:09:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:10:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:10:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:10:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:11:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:11:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:11:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:12:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:12:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:12:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:13:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:13:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:14:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:14:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:15:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:15:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:16:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:17:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:17:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:18:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:18:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:18:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:19:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:19:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:19:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:20:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:20:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:21:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:21:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:22:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:22:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:23:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:23:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:24:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:24:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:25:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:25:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:25:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:26:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:27:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:27:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:28:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:28:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:28:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:29:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:29:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:29:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:30:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:30:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:31:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:31:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:31:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:32:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:32:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:32:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:33:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:33:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:33:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:34:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:34:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:34:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:35:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:35:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:35:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:36:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:36:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:37:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:37:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:38:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:38:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:39:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:39:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:39:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:40:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:41:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:41:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:41:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:42:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:42:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:43:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:44:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:44:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:45:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:45:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:45:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:46:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:46:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:46:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:47:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:48:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:48:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:49:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:49:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:49:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:50:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:50:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:51:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:51:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:52:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:52:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:52:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:53:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:53:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:53:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:54:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:54:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:54:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:55:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:55:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:55:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:56:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:56:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:57:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:57:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:57:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:58:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:58:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 23:59:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 00:00:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 00:00:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 00:01:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 00:01:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 00:01:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 00:01:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 00:02:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 00:02:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 00:03:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 00:03:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 00:04:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 00:04:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 00:04:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 00:04:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 00:04:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 00:05:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 00:06:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 00:06:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 00:06:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 00:07:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 00:07:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 00:07:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 00:08:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 00:08:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 00:08:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 00:08:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 00:09:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 00:09:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 00:10:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 00:11:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 00:11:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 00:12:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 00:12:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 00:13:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 00:13:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 00:14:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 00:15:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 00:16:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 00:16:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 00:17:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 00:17:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 00:18:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 00:19:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 00:20:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 00:21:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 16:18:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 16:19:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 16:19:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 16:19:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 16:19:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 16:20:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 16:20:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 16:21:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 16:21:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 16:22:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 16:22:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 16:23:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 16:23:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 16:24:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 16:24:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 16:25:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 16:25:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 16:25:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 16:25:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 16:26:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 16:26:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 16:27:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 16:27:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 16:28:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 16:28:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 16:29:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 16:30:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 16:31:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 17:42:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 17:42:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 17:43:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 17:43:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 17:43:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 17:43:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 17:44:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 17:44:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 17:44:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 17:45:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 17:46:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 17:46:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 17:46:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 04 17:47:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 16:56:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 16:57:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 16:57:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 16:57:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 16:58:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 16:58:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 16:58:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 16:59:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 16:59:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 16:59:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 17:00:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 17:00:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 17:00:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 17:01:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 17:01:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 17:01:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 17:02:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 17:03:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 17:03:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 17:04:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 17:05:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 17:05:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 17:05:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 17:06:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 17:06:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 17:07:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 17:08:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 17:08:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 17:08:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 17:09:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 17:09:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 17:10:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 17:10:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 17:10:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 17:11:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 17:11:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 17:11:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 17:12:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 17:13:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 17:14:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 17:14:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 17:14:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 17:15:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 17:15:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 17:16:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 17:16:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 17:16:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 17:17:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 17:17:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 17:17:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 17:18:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 17:19:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 17:19:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 17:20:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 17:21:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 17:21:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 17:21:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 17:22:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 17:22:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 17:22:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 17:23:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 17:23:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 17:24:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 17:24:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 17:25:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 17:25:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 17:26:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 17:26:47 EDT 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -931,16 +2522,16 @@
   <dimension ref="A1:I8"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="26.73046875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="9.19921875" style="1" collapsed="1"/>
-    <col min="4" max="4" width="44.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="35.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="15.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="17.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="19.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="40.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="10" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.73046875" collapsed="true"/>
+    <col min="3" max="3" style="1" width="9.19921875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="44.53125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="35.53125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="1" width="15.265625" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="1" width="17.265625" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="19.53125" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="1" width="40.19921875" collapsed="true"/>
+    <col min="10" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
@@ -974,7 +2565,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>67</v>
+        <v>624</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -986,7 +2577,7 @@
         <v>8</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>19</v>
@@ -997,10 +2588,10 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
-        <v>35</v>
+        <v>151</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>68</v>
+        <v>625</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -1012,7 +2603,7 @@
         <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>20</v>
@@ -1026,7 +2617,7 @@
         <v>35</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>156</v>
+        <v>626</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -1038,7 +2629,7 @@
         <v>10</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>21</v>
@@ -1052,7 +2643,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>69</v>
+        <v>627</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -1064,7 +2655,7 @@
         <v>11</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>22</v>
@@ -1078,7 +2669,7 @@
         <v>35</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>70</v>
+        <v>628</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -1090,7 +2681,7 @@
         <v>12</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>23</v>
@@ -1101,10 +2692,10 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
-        <v>35</v>
+        <v>151</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>157</v>
+        <v>629</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -1116,7 +2707,7 @@
         <v>13</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>24</v>
@@ -1130,7 +2721,7 @@
         <v>35</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>71</v>
+        <v>630</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>32</v>
@@ -1142,7 +2733,7 @@
         <v>57</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>53</v>
@@ -1163,16 +2754,16 @@
   <dimension ref="A1:J21"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="14.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="26.73046875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="17.06640625" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="51.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="32.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="7" width="9.19921875" style="1" collapsed="1"/>
-    <col min="8" max="8" width="18" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="29.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="52.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="11" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" customWidth="true" style="1" width="14.53125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.73046875" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="17.06640625" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="51.73046875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="32.46484375" collapsed="true"/>
+    <col min="6" max="7" style="1" width="9.19921875" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="18.0" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="1" width="29.19921875" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="1" width="52.46484375" collapsed="true"/>
+    <col min="11" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
@@ -1206,7 +2797,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>72</v>
+        <v>254</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -1226,7 +2817,7 @@
         <v>35</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>73</v>
+        <v>255</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -1246,7 +2837,7 @@
         <v>35</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>74</v>
+        <v>256</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -1266,7 +2857,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>75</v>
+        <v>257</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -1286,7 +2877,7 @@
         <v>35</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>76</v>
+        <v>258</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -1306,7 +2897,7 @@
         <v>35</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>77</v>
+        <v>259</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -1329,7 +2920,7 @@
         <v>35</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>78</v>
+        <v>260</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>32</v>
@@ -1349,10 +2940,10 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
-        <v>35</v>
+        <v>151</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>79</v>
+        <v>261</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>32</v>
@@ -1372,10 +2963,10 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
-        <v>35</v>
+        <v>151</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>80</v>
+        <v>262</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>32</v>
@@ -1398,7 +2989,7 @@
         <v>35</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>81</v>
+        <v>263</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>32</v>
@@ -1415,10 +3006,10 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
-        <v>35</v>
+        <v>151</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>82</v>
+        <v>264</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>32</v>
@@ -1438,7 +3029,7 @@
         <v>35</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>83</v>
+        <v>265</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>32</v>
@@ -1458,10 +3049,10 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
-        <v>35</v>
+        <v>151</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>84</v>
+        <v>266</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>32</v>
@@ -1484,7 +3075,7 @@
         <v>35</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>85</v>
+        <v>267</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>32</v>
@@ -1504,7 +3095,7 @@
         <v>35</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>86</v>
+        <v>268</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>32</v>
@@ -1527,7 +3118,7 @@
         <v>35</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>87</v>
+        <v>269</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>32</v>
@@ -1547,10 +3138,10 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
-        <v>35</v>
+        <v>151</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>88</v>
+        <v>270</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>32</v>
@@ -1584,7 +3175,7 @@
         <v>35</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>89</v>
+        <v>271</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>32</v>
@@ -1599,7 +3190,7 @@
         <v>59</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.45">
@@ -1616,7 +3207,7 @@
         <v>32</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -1632,16 +3223,16 @@
   <dimension ref="A1:I7"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="35" style="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="24.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="24.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="27" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
-    <col min="7" max="7" width="17" style="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="16.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="48.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="10" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="1" width="35.0" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="24.19921875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="24.46484375" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="27.0" collapsed="true"/>
+    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="1" width="17.0" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="16.265625" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="1" width="48.46484375" collapsed="true"/>
+    <col min="10" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
@@ -1675,7 +3266,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>90</v>
+        <v>290</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -1698,10 +3289,10 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
-        <v>35</v>
+        <v>151</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>91</v>
+        <v>291</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -1724,7 +3315,7 @@
         <v>35</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>92</v>
+        <v>292</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -1744,10 +3335,10 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
-        <v>35</v>
+        <v>151</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>93</v>
+        <v>293</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -1767,10 +3358,10 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
-        <v>35</v>
+        <v>151</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>94</v>
+        <v>294</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -1790,10 +3381,10 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
-        <v>35</v>
+        <v>151</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>95</v>
+        <v>295</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -1825,19 +3416,19 @@
   <dimension ref="A1:L64"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="30.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="13.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="31.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="38.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
-    <col min="7" max="7" width="19.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="9.19921875" style="1" collapsed="1"/>
-    <col min="9" max="9" width="15.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="13.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="13.265625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="70.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="13" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="1" width="30.265625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="13.265625" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="31.73046875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="38.73046875" collapsed="true"/>
+    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="1" width="19.796875" collapsed="true"/>
+    <col min="8" max="8" style="1" width="9.19921875" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="1" width="15.73046875" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="1" width="13.265625" collapsed="true"/>
+    <col min="11" max="11" customWidth="true" style="1" width="13.265625"/>
+    <col min="12" max="12" customWidth="true" style="1" width="70.73046875" collapsed="true"/>
+    <col min="13" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.45">
@@ -1872,7 +3463,7 @@
         <v>55</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.45">
@@ -1880,7 +3471,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>96</v>
+        <v>631</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -1903,7 +3494,7 @@
         <v>35</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>97</v>
+        <v>632</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -1926,7 +3517,7 @@
         <v>35</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>98</v>
+        <v>633</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -1949,7 +3540,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>99</v>
+        <v>634</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -1972,7 +3563,7 @@
         <v>35</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>100</v>
+        <v>635</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -1995,7 +3586,7 @@
         <v>35</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>101</v>
+        <v>636</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -2018,7 +3609,7 @@
         <v>35</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>102</v>
+        <v>637</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>32</v>
@@ -2041,7 +3632,7 @@
         <v>35</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>103</v>
+        <v>638</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>32</v>
@@ -2064,7 +3655,7 @@
         <v>35</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>104</v>
+        <v>639</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>32</v>
@@ -2087,7 +3678,7 @@
         <v>35</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>105</v>
+        <v>640</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>32</v>
@@ -2110,7 +3701,7 @@
         <v>35</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>106</v>
+        <v>641</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>32</v>
@@ -2133,7 +3724,7 @@
         <v>35</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>107</v>
+        <v>642</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>32</v>
@@ -2156,7 +3747,7 @@
         <v>35</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>108</v>
+        <v>643</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>32</v>
@@ -2179,7 +3770,7 @@
         <v>35</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>109</v>
+        <v>644</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>32</v>
@@ -2202,7 +3793,7 @@
         <v>35</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>110</v>
+        <v>645</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>32</v>
@@ -2222,10 +3813,10 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
-        <v>35</v>
+        <v>151</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>111</v>
+        <v>646</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>32</v>
@@ -2237,7 +3828,7 @@
         <v>38</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>32</v>
@@ -2254,7 +3845,7 @@
         <v>35</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>112</v>
+        <v>647</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>32</v>
@@ -2266,7 +3857,7 @@
         <v>29</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>32</v>
@@ -2280,10 +3871,10 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
-        <v>35</v>
+        <v>151</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>113</v>
+        <v>648</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>32</v>
@@ -2295,7 +3886,7 @@
         <v>25</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>32</v>
@@ -2312,7 +3903,7 @@
         <v>35</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>114</v>
+        <v>649</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>32</v>
@@ -2332,10 +3923,10 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
-        <v>35</v>
+        <v>151</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>168</v>
+        <v>650</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>32</v>
@@ -2347,7 +3938,7 @@
         <v>40</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>49</v>
@@ -2364,7 +3955,7 @@
         <v>35</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>115</v>
+        <v>651</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>32</v>
@@ -2376,7 +3967,7 @@
         <v>46</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>32</v>
@@ -2393,7 +3984,7 @@
         <v>35</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>116</v>
+        <v>652</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>32</v>
@@ -2405,7 +3996,7 @@
         <v>41</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>32</v>
@@ -2419,7 +4010,7 @@
         <v>35</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>117</v>
+        <v>653</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>32</v>
@@ -2431,7 +4022,7 @@
         <v>27</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>32</v>
@@ -2445,10 +4036,10 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="s">
-        <v>35</v>
+        <v>151</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>118</v>
+        <v>654</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>32</v>
@@ -2460,7 +4051,7 @@
         <v>42</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>32</v>
@@ -2477,7 +4068,7 @@
         <v>35</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>119</v>
+        <v>655</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>32</v>
@@ -2489,7 +4080,7 @@
         <v>43</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>32</v>
@@ -2503,10 +4094,10 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A27" s="1" t="s">
-        <v>35</v>
+        <v>151</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>120</v>
+        <v>656</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>32</v>
@@ -2518,7 +4109,7 @@
         <v>44</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>32</v>
@@ -2532,7 +4123,7 @@
         <v>35</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>121</v>
+        <v>657</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>32</v>
@@ -2544,7 +4135,7 @@
         <v>28</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>32</v>
@@ -2561,7 +4152,7 @@
         <v>35</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>122</v>
+        <v>658</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>32</v>
@@ -2590,7 +4181,7 @@
         <v>35</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>123</v>
+        <v>659</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>32</v>
@@ -2616,10 +4207,10 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A31" s="1" t="s">
-        <v>35</v>
+        <v>151</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>124</v>
+        <v>660</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>32</v>
@@ -2648,7 +4239,7 @@
         <v>35</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>125</v>
+        <v>661</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>32</v>
@@ -2668,10 +4259,10 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A33" s="1" t="s">
-        <v>160</v>
+        <v>35</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>161</v>
+        <v>662</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>32</v>
@@ -2700,7 +4291,7 @@
         <v>35</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>126</v>
+        <v>663</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>32</v>
@@ -2729,7 +4320,7 @@
         <v>35</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>127</v>
+        <v>664</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>32</v>
@@ -2755,7 +4346,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>128</v>
+        <v>665</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>32</v>
@@ -2784,7 +4375,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>129</v>
+        <v>666</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>32</v>
@@ -2810,10 +4401,10 @@
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A38" s="1" t="s">
-        <v>35</v>
+        <v>151</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>130</v>
+        <v>667</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>32</v>
@@ -2839,10 +4430,10 @@
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A39" s="1" t="s">
-        <v>35</v>
+        <v>151</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>131</v>
+        <v>668</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>32</v>
@@ -2868,7 +4459,7 @@
         <v>35</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>132</v>
+        <v>669</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>32</v>
@@ -2897,7 +4488,7 @@
         <v>35</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>133</v>
+        <v>670</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>32</v>
@@ -2926,7 +4517,7 @@
         <v>35</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>134</v>
+        <v>671</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>32</v>
@@ -2955,7 +4546,7 @@
         <v>35</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>135</v>
+        <v>672</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>32</v>
@@ -2984,7 +4575,7 @@
         <v>35</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>136</v>
+        <v>673</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>32</v>
@@ -3004,10 +4595,10 @@
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A45" s="1" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>162</v>
+        <v>674</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>32</v>
@@ -3036,7 +4627,7 @@
         <v>35</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>137</v>
+        <v>675</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>32</v>
@@ -3065,7 +4656,7 @@
         <v>35</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>138</v>
+        <v>676</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>32</v>
@@ -3091,7 +4682,7 @@
         <v>35</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>163</v>
+        <v>677</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>32</v>
@@ -3120,7 +4711,7 @@
         <v>35</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>139</v>
+        <v>678</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>32</v>
@@ -3149,7 +4740,7 @@
         <v>35</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>140</v>
+        <v>679</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>32</v>
@@ -3175,10 +4766,10 @@
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A51" s="1" t="s">
-        <v>35</v>
+        <v>151</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>141</v>
+        <v>680</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>32</v>
@@ -3204,7 +4795,7 @@
         <v>35</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>142</v>
+        <v>681</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>32</v>
@@ -3233,7 +4824,7 @@
         <v>35</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>143</v>
+        <v>682</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>32</v>
@@ -3245,15 +4836,21 @@
         <v>57</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A54" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>683</v>
+      </c>
       <c r="C54" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>16</v>
@@ -3262,13 +4859,13 @@
         <v>58</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>32</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.45">
@@ -3282,7 +4879,7 @@
         <v>45</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>32</v>
@@ -3296,7 +4893,7 @@
         <v>35</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>164</v>
+        <v>684</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>32</v>
@@ -3311,12 +4908,18 @@
         <v>56</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A57" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>685</v>
+      </c>
       <c r="C57" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>16</v>
@@ -3331,7 +4934,7 @@
         <v>32</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.45">
@@ -3359,7 +4962,7 @@
         <v>35</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>144</v>
+        <v>686</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>32</v>
@@ -3374,12 +4977,18 @@
         <v>37</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A60" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>687</v>
+      </c>
       <c r="C60" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>16</v>
@@ -3394,7 +5003,7 @@
         <v>32</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.45">
@@ -3422,7 +5031,7 @@
         <v>35</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>165</v>
+        <v>688</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>32</v>
@@ -3431,10 +5040,10 @@
         <v>16</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>52</v>
@@ -3448,7 +5057,7 @@
         <v>35</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>166</v>
+        <v>689</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>32</v>
@@ -3457,7 +5066,7 @@
         <v>16</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>56</v>
@@ -3471,10 +5080,10 @@
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A64" s="1" t="s">
-        <v>35</v>
+        <v>151</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>167</v>
+        <v>690</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>32</v>
@@ -3483,7 +5092,7 @@
         <v>16</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>37</v>
@@ -3496,7 +5105,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="E1:E52" xr:uid="{E3B7105E-5E71-456F-8D2A-C4C503B29111}"/>
+  <autoFilter ref="E1:E64" xr:uid="{E3B7105E-5E71-456F-8D2A-C4C503B29111}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
   <headerFooter>
@@ -3510,12 +5119,12 @@
   <dimension ref="A1:F7"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="22.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="23" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="1" width="22.46484375" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="23.0" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
+    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
@@ -3617,12 +5226,12 @@
   <dimension ref="A1:F9"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="26.46484375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="14.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.46484375" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="14.46484375" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
+    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
@@ -3650,7 +5259,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>146</v>
+        <v>691</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -3662,7 +5271,7 @@
         <v>17</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
@@ -3670,7 +5279,7 @@
         <v>35</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>147</v>
+        <v>692</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -3687,10 +5296,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
-        <v>35</v>
+        <v>151</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>148</v>
+        <v>693</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -3710,7 +5319,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>149</v>
+        <v>694</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -3727,10 +5336,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
-        <v>35</v>
+        <v>151</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>150</v>
+        <v>695</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -3750,10 +5359,10 @@
         <v>35</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>62</v>
+        <v>696</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>16</v>
@@ -3762,18 +5371,18 @@
         <v>39</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
-        <v>35</v>
+        <v>151</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>63</v>
+        <v>697</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>16</v>
@@ -3782,18 +5391,18 @@
         <v>39</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
-        <v>35</v>
+        <v>151</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>64</v>
+        <v>698</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>16</v>
@@ -3802,7 +5411,7 @@
         <v>39</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -3815,12 +5424,12 @@
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="27.73046875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="17" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.73046875" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="17.0" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
+    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
@@ -3845,10 +5454,10 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
-        <v>35</v>
+        <v>151</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>151</v>
+        <v>584</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -3860,15 +5469,15 @@
         <v>17</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
-        <v>35</v>
+        <v>151</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>152</v>
+        <v>585</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -3888,7 +5497,7 @@
         <v>35</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>153</v>
+        <v>586</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -3905,10 +5514,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
-        <v>35</v>
+        <v>151</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>154</v>
+        <v>587</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -3925,10 +5534,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
-        <v>35</v>
+        <v>151</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>155</v>
+        <v>588</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -3953,12 +5562,12 @@
   <dimension ref="A1:E3"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="26" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="15.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.0" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="15.796875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
+    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
@@ -3983,7 +5592,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>145</v>
+        <v>536</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
